--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_SCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_SCF_Demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833B9275-C533-4F9F-88A7-8374CA16FB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0CF60E-84D6-47C6-92A4-BD241E16951D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="74">
   <si>
     <t>Result</t>
   </si>
@@ -296,141 +296,6 @@
 Company Name:,	Vaddahun Corp,
 First Name:,	DULIP,
 Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Monthly,
-Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
 Routing Number:,	****2691,
 Account Number:,	****5489,
 Billing Address:,	708 36TH AVE NW,,
@@ -441,106 +306,6 @@
 Payment Plan Type:,	Automatic Payment 
 Payment Plan Start Date:,	
 4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -665,46 +430,46 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Fri Jul 03 20:38:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:39:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:40:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:41:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:42:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:42:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:49:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:50:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:51:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:51:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:52:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:53:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:53:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 19:47:04 IST 2026</t>
+    <t>Wed Oct 07 23:21:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:24:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:25:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:26:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:26:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:27:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:41:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:53:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:53:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:54:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:55:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:56:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:57:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 19:52:36 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -731,15 +496,42 @@
 Payment Plan Type:,	Installment Plan,_x000D_
 Payment Plan Duration:,	Daily,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+4. Payment Plan,1 Daily payment of $</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Daily payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	_x000D_
 Total Convenience Fees Paid:,	_x000D_
 Total Paid under this plan:</t>
   </si>
   <si>
-    <t>Wed Jul 29 19:50:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 20:10:24 IST 2026</t>
+    <t>Wed Oct 14 16:08:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:02:36 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -766,12 +558,10 @@
 Payment Plan Type:,	Installment Plan,_x000D_
 Payment Plan Duration:,	Deferred,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 20:29:11 IST 2026</t>
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:06:59 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -798,12 +588,10 @@
 Payment Plan Type:,	Recurring,_x000D_
 Payment Plan Duration:,	Daily,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan, Daily payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 20:36:39 IST 2026</t>
+4. Payment Plan, Daily payments of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:11:32 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -830,12 +618,10 @@
 Payment Plan Type:,	Recurring,_x000D_
 Payment Plan Duration:,	Deferred,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 20:39:45 IST 2026</t>
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:14:52 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -862,15 +648,10 @@
 Payment Plan Type:,	Recurring,_x000D_
 Payment Plan Duration:,	Monthly,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 20:43:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 21:11:27 IST 2026</t>
+4. Payment Plan,Monthly payments of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:19:24 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -895,15 +676,13 @@
 Payment Plan Type:,	Installment Plan,_x000D_
 Payment Plan Duration:,	Daily,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 21:16:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 21:19:17 IST 2026</t>
+4. Payment Plan,1 Daily payment of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:23:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:27:21 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -928,12 +707,10 @@
 Payment Plan Type:,	Installment Plan,_x000D_
 Payment Plan Duration:,	Deferred,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 21:24:09 IST 2026</t>
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:30:16 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -958,12 +735,10 @@
 Payment Plan Type:,	Recurring,_x000D_
 Payment Plan Duration:,	Daily,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan, Daily payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 21:26:47 IST 2026</t>
+4. Payment Plan, Daily payments of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:32:58 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,_x000D_
@@ -988,12 +763,13 @@
 Payment Plan Type:,	Recurring,_x000D_
 Payment Plan Duration:,	Deferred,_x000D_
 Payment Plan Start Date:,	_x000D_
-4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
-Total Convenience Fees Paid:,	_x000D_
-Total Paid under this plan:</t>
-  </si>
-  <si>
-    <t>Wed Jul 29 21:41:06 IST 2026</t>
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:36:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 14 17:37:56 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1214,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1464,11 +1240,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1476,14 +1252,41 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>61</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Daily payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1559,7 +1362,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1585,11 +1388,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1620,7 +1423,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1628,7 +1431,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1701,7 +1504,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1727,11 +1530,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1739,14 +1542,39 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>78</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan, Daily payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1819,7 +1647,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1845,11 +1673,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1857,14 +1685,41 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>66</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan, Daily payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1937,7 +1792,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1967,7 +1822,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1998,7 +1853,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2006,7 +1861,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2081,7 +1936,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2107,11 +1962,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2143,7 +1998,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2151,7 +2006,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2224,7 +2079,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2250,11 +2105,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2262,14 +2117,39 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>76</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Deferred,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Deferred payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2342,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2372,7 +2252,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2403,7 +2283,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2411,7 +2291,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2484,7 +2364,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2510,11 +2390,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2522,14 +2402,41 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>64</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Deferred,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Deferred payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2602,7 +2509,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2628,11 +2535,11 @@
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2664,7 +2571,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2672,7 +2579,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2745,7 +2652,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2771,11 +2678,11 @@
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2783,14 +2690,39 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>73</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Daily payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2863,7 +2795,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2893,7 +2825,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2979,7 +2911,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3009,7 +2941,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3040,7 +2972,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3048,7 +2980,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3063,7 +2995,8 @@
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" customWidth="true" width="20.36328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="27.6328125" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" width="12.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -3121,7 +3054,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3147,11 +3080,11 @@
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3160,13 +3093,13 @@
         <v>2</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3239,7 +3172,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3269,7 +3202,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3300,7 +3233,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3308,7 +3241,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3381,7 +3314,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3407,11 +3340,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3419,14 +3352,39 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>73</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Daily payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3499,7 +3457,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3525,11 +3483,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3561,7 +3519,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3569,7 +3527,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3642,7 +3600,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3668,11 +3626,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3680,14 +3638,41 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>70</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Monthly,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,Monthly payments of $10.00 starting on 10/15/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3763,7 +3748,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3789,11 +3774,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3879,7 +3864,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3905,11 +3890,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3995,7 +3980,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4025,7 +4010,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4111,7 +4096,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4137,11 +4122,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4173,7 +4158,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4181,7 +4166,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4254,7 +4239,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4280,11 +4265,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4292,14 +4277,39 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>80</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Deferred,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Deferred payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4372,7 +4382,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4398,11 +4408,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4410,14 +4420,41 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>68</v>
+      <c r="O2" s="9" t="str">
+        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
+        <v>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Deferred,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Deferred payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4490,7 +4527,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4520,7 +4557,7 @@
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/30/2026</v>
+        <v>10/15/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4551,7 +4588,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 10/15/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4559,7 +4596,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/15/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
